--- a/diseases/d064/1995-1999.xlsx
+++ b/diseases/d064/1995-1999.xlsx
@@ -761,9 +761,6 @@
       <c r="O2" t="n">
         <v>0</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
       <c r="S2" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -1146,9 +1143,6 @@
       <c r="O4" t="n">
         <v>0</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="S4" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -1529,9 +1523,6 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="S6" t="inlineStr">
